--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>10.326199054718018</v>
+        <v>9.98130178451538</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>9.98130178451538</v>
+        <v>10.015254020690918</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>10.015254020690918</v>
+        <v>9.38119912147522</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>9.38119912147522</v>
+        <v>8.974870204925537</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>8.974870204925537</v>
+        <v>4.529386043548584</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>4.529386043548584</v>
+        <v>4.64819598197937</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -498,25 +498,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.5766407371615079</v>
+        <v>0.577168739983999</v>
       </c>
       <c r="C2">
-        <v>0.15850412295899913</v>
+        <v>0.2082565988873654</v>
       </c>
       <c r="D2">
-        <v>3.6380172729681597</v>
+        <v>2.7714307400946177</v>
       </c>
       <c r="E2">
-        <v>0.00027474500308088956</v>
+        <v>0.00558105439189549</v>
       </c>
       <c r="F2">
-        <v>0.1950175752517572</v>
+        <v>0.22649460835938037</v>
       </c>
       <c r="G2">
-        <v>2.956865484647195</v>
+        <v>2.5482670168828117</v>
       </c>
       <c r="H2">
-        <v>0.0031078366667198765</v>
+        <v>0.010825957286000776</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -550,25 +550,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.2061558129390777</v>
+        <v>-0.3033520570432794</v>
       </c>
       <c r="C4">
-        <v>0.19392672869945757</v>
+        <v>0.24168969255889336</v>
       </c>
       <c r="D4">
-        <v>-1.0630603337746827</v>
+        <v>-1.25513030295804</v>
       </c>
       <c r="E4">
-        <v>0.28775459128134173</v>
+        <v>0.20943146156121473</v>
       </c>
       <c r="F4">
-        <v>0.2656690484090448</v>
+        <v>0.33742398454460953</v>
       </c>
       <c r="G4">
-        <v>-0.7759873202152782</v>
+        <v>-0.899023397677809</v>
       </c>
       <c r="H4">
-        <v>0.4377564726142711</v>
+        <v>0.3686401980251146</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -576,22 +576,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-5.893672550416554</v>
+        <v>-5.99137687352073</v>
       </c>
       <c r="C5">
-        <v>0.2794321457756981</v>
+        <v>0.3106217992779045</v>
       </c>
       <c r="D5">
-        <v>-21.091605384397834</v>
+        <v>-19.28833355369375</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.45251958917948243</v>
+        <v>0.3868056646131152</v>
       </c>
       <c r="G5">
-        <v>-13.02412689161828</v>
+        <v>-15.489372110186991</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -602,22 +602,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>4.049598663667698</v>
+        <v>4.140604401662334</v>
       </c>
       <c r="C6">
-        <v>0.22884593943178713</v>
+        <v>0.2984300374397598</v>
       </c>
       <c r="D6">
-        <v>17.695741832792166</v>
+        <v>13.874623470159715</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.29536689977558617</v>
+        <v>0.4675725351994287</v>
       </c>
       <c r="G6">
-        <v>13.710401086731459</v>
+        <v>8.855533826203642</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -628,25 +628,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1.0518665153574638</v>
+        <v>1.4303666303531601</v>
       </c>
       <c r="C7">
-        <v>0.16566012285879256</v>
+        <v>0.2694228523271738</v>
       </c>
       <c r="D7">
-        <v>6.349545667390739</v>
+        <v>5.309002625420184</v>
       </c>
       <c r="E7">
-        <v>2.1595170096588845e-10</v>
+        <v>1.1022674595295712e-7</v>
       </c>
       <c r="F7">
-        <v>0.24241803727094227</v>
+        <v>0.41441611492837127</v>
       </c>
       <c r="G7">
-        <v>4.339060439557263</v>
+        <v>3.4515227058686855</v>
       </c>
       <c r="H7">
-        <v>1.4309316857641363e-5</v>
+        <v>0.0005574328517876648</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -654,25 +654,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>2.3185427749973573</v>
+        <v>1.8616371517017085</v>
       </c>
       <c r="C8">
-        <v>0.2094337658320488</v>
+        <v>0.27073718440246575</v>
       </c>
       <c r="D8">
-        <v>11.07052993955457</v>
+        <v>6.876178297452788</v>
       </c>
       <c r="E8">
-        <v>0.0</v>
+        <v>6.147971021164267e-12</v>
       </c>
       <c r="F8">
-        <v>0.2876187205146617</v>
+        <v>0.3677157927409843</v>
       </c>
       <c r="G8">
-        <v>8.061167822624977</v>
+        <v>5.062706547969858</v>
       </c>
       <c r="H8">
-        <v>6.661338147750939e-16</v>
+        <v>4.133458491040187e-7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -680,22 +680,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>3.1444638439388943</v>
+        <v>4.212325724552624</v>
       </c>
       <c r="C9">
-        <v>0.1566061331578166</v>
+        <v>0.23564292467943546</v>
       </c>
       <c r="D9">
-        <v>20.078803942947278</v>
+        <v>17.875884583774365</v>
       </c>
       <c r="E9">
         <v>0.0</v>
       </c>
       <c r="F9">
-        <v>0.26098546654719645</v>
+        <v>0.2841293769618229</v>
       </c>
       <c r="G9">
-        <v>12.048425092553003</v>
+        <v>14.825379091717835</v>
       </c>
       <c r="H9">
         <v>0.0</v>
@@ -706,22 +706,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>-3.2411031418527076</v>
+        <v>-3.409992114458849</v>
       </c>
       <c r="C10">
-        <v>0.17757900373903465</v>
+        <v>0.19677695027595113</v>
       </c>
       <c r="D10">
-        <v>-18.251612373137007</v>
+        <v>-17.32922534715997</v>
       </c>
       <c r="E10">
         <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.2767064305387596</v>
+        <v>0.3916049080334629</v>
       </c>
       <c r="G10">
-        <v>-11.713147163013657</v>
+        <v>-8.707735895300534</v>
       </c>
       <c r="H10">
         <v>0.0</v>
@@ -742,7 +742,7 @@
         <v>17</v>
       </c>
       <c r="B1">
-        <v>-3612.2983925504764</v>
+        <v>-3585.8615589522547</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -758,7 +758,7 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>4.64819598197937</v>
+        <v>19.88916802406311</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -806,7 +806,7 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>7240.596785100953</v>
+        <v>7187.723117904509</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -814,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>7295.1564723112415</v>
+        <v>7242.282805114798</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -822,7 +822,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>0.4813390966162969</v>
+        <v>0.48513494914745425</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>19.88916802406311</v>
+        <v>16.058441877365112</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>16.058441877365112</v>
+        <v>11.820130825042725</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -498,25 +498,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.577168739983999</v>
+        <v>0.5771687565083803</v>
       </c>
       <c r="C2">
-        <v>0.2082565988873654</v>
+        <v>0.20825659915938108</v>
       </c>
       <c r="D2">
-        <v>2.7714307400946177</v>
+        <v>2.771430815820951</v>
       </c>
       <c r="E2">
-        <v>0.00558105439189549</v>
+        <v>0.0055810530937712155</v>
       </c>
       <c r="F2">
-        <v>0.22649460835938037</v>
+        <v>0.22649460752239955</v>
       </c>
       <c r="G2">
-        <v>2.5482670168828117</v>
+        <v>2.5482670992566576</v>
       </c>
       <c r="H2">
-        <v>0.010825957286000776</v>
+        <v>0.010825954729488219</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -550,25 +550,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.3033520570432794</v>
+        <v>-0.30335202298546954</v>
       </c>
       <c r="C4">
-        <v>0.24168969255889336</v>
+        <v>0.24168968892516354</v>
       </c>
       <c r="D4">
-        <v>-1.25513030295804</v>
+        <v>-1.2551301809130924</v>
       </c>
       <c r="E4">
-        <v>0.20943146156121473</v>
+        <v>0.20943150585844217</v>
       </c>
       <c r="F4">
-        <v>0.33742398454460953</v>
+        <v>0.3374239790494911</v>
       </c>
       <c r="G4">
-        <v>-0.899023397677809</v>
+        <v>-0.8990233113840906</v>
       </c>
       <c r="H4">
-        <v>0.3686401980251146</v>
+        <v>0.3686402439884471</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -576,22 +576,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-5.99137687352073</v>
+        <v>-5.991376898154346</v>
       </c>
       <c r="C5">
-        <v>0.3106217992779045</v>
+        <v>0.31062179905761816</v>
       </c>
       <c r="D5">
-        <v>-19.28833355369375</v>
+        <v>-19.288333646676833</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.3868056646131152</v>
+        <v>0.38680566413659484</v>
       </c>
       <c r="G5">
-        <v>-15.489372110186991</v>
+        <v>-15.489372192953663</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -602,22 +602,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>4.140604401662334</v>
+        <v>4.140604416611269</v>
       </c>
       <c r="C6">
-        <v>0.2984300374397598</v>
+        <v>0.2984300371062786</v>
       </c>
       <c r="D6">
-        <v>13.874623470159715</v>
+        <v>13.874623535755864</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.4675725351994287</v>
+        <v>0.46757252980287445</v>
       </c>
       <c r="G6">
-        <v>8.855533826203642</v>
+        <v>8.855533960382404</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -628,25 +628,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1.4303666303531601</v>
+        <v>1.4303666361999972</v>
       </c>
       <c r="C7">
-        <v>0.2694228523271738</v>
+        <v>0.269422850228147</v>
       </c>
       <c r="D7">
-        <v>5.309002625420184</v>
+        <v>5.309002688483045</v>
       </c>
       <c r="E7">
-        <v>1.1022674595295712e-7</v>
+        <v>1.1022670776128507e-7</v>
       </c>
       <c r="F7">
-        <v>0.41441611492837127</v>
+        <v>0.41441610842772164</v>
       </c>
       <c r="G7">
-        <v>3.4515227058686855</v>
+        <v>3.4515227741188723</v>
       </c>
       <c r="H7">
-        <v>0.0005574328517876648</v>
+        <v>0.0005574327108044397</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -654,25 +654,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1.8616371517017085</v>
+        <v>1.8616371281626956</v>
       </c>
       <c r="C8">
-        <v>0.27073718440246575</v>
+        <v>0.270737175351567</v>
       </c>
       <c r="D8">
-        <v>6.876178297452788</v>
+        <v>6.876178440383217</v>
       </c>
       <c r="E8">
         <v>6.147971021164267e-12</v>
       </c>
       <c r="F8">
-        <v>0.3677157927409843</v>
+        <v>0.3677157724929804</v>
       </c>
       <c r="G8">
-        <v>5.062706547969858</v>
+        <v>5.062706762729993</v>
       </c>
       <c r="H8">
-        <v>4.133458491040187e-7</v>
+        <v>4.133453832544376e-7</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -680,22 +680,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>4.212325724552624</v>
+        <v>4.212325735986811</v>
       </c>
       <c r="C9">
-        <v>0.23564292467943546</v>
+        <v>0.2356429252239392</v>
       </c>
       <c r="D9">
-        <v>17.875884583774365</v>
+        <v>17.875884590991642</v>
       </c>
       <c r="E9">
         <v>0.0</v>
       </c>
       <c r="F9">
-        <v>0.2841293769618229</v>
+        <v>0.28412937930333726</v>
       </c>
       <c r="G9">
-        <v>14.825379091717835</v>
+        <v>14.825379009784557</v>
       </c>
       <c r="H9">
         <v>0.0</v>
@@ -706,22 +706,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>-3.409992114458849</v>
+        <v>-3.4099921099535893</v>
       </c>
       <c r="C10">
-        <v>0.19677695027595113</v>
+        <v>0.1967769508018489</v>
       </c>
       <c r="D10">
-        <v>-17.32922534715997</v>
+        <v>-17.329225277951352</v>
       </c>
       <c r="E10">
         <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.3916049080334629</v>
+        <v>0.39160490863572234</v>
       </c>
       <c r="G10">
-        <v>-8.707735895300534</v>
+        <v>-8.707735870404074</v>
       </c>
       <c r="H10">
         <v>0.0</v>
@@ -742,7 +742,7 @@
         <v>17</v>
       </c>
       <c r="B1">
-        <v>-3585.8615589522547</v>
+        <v>-3585.8615589522515</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>11.820130825042725</v>
+        <v>6.527347087860107</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -806,7 +806,7 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>7187.723117904509</v>
+        <v>7187.723117904503</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -814,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>7242.282805114798</v>
+        <v>7242.282805114792</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -822,7 +822,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>0.48513494914745425</v>
+        <v>0.4851349491474547</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -498,25 +498,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.5771687565083803</v>
+        <v>0.5413382749470123</v>
       </c>
       <c r="C2">
-        <v>0.20825659915938108</v>
+        <v>0.20789108233408615</v>
       </c>
       <c r="D2">
-        <v>2.771430815820951</v>
+        <v>2.603951400267704</v>
       </c>
       <c r="E2">
-        <v>0.0055810530937712155</v>
+        <v>0.0092155823488842</v>
       </c>
       <c r="F2">
-        <v>0.22649460752239955</v>
+        <v>0.2220848457579025</v>
       </c>
       <c r="G2">
-        <v>2.5482670992566576</v>
+        <v>2.437529103346079</v>
       </c>
       <c r="H2">
-        <v>0.010825954729488219</v>
+        <v>0.01478802378150057</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -550,25 +550,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>-0.30335202298546954</v>
+        <v>-0.23615110086335528</v>
       </c>
       <c r="C4">
-        <v>0.24168968892516354</v>
+        <v>0.16571284845570794</v>
       </c>
       <c r="D4">
-        <v>-1.2551301809130924</v>
+        <v>-1.4250621063126208</v>
       </c>
       <c r="E4">
-        <v>0.20943150585844217</v>
+        <v>0.15413924913998978</v>
       </c>
       <c r="F4">
-        <v>0.3374239790494911</v>
+        <v>0.1740504743799203</v>
       </c>
       <c r="G4">
-        <v>-0.8990233113840906</v>
+        <v>-1.3567966516878356</v>
       </c>
       <c r="H4">
-        <v>0.3686402439884471</v>
+        <v>0.17484583171065893</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -576,22 +576,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>-5.991376898154346</v>
+        <v>-6.093277451092545</v>
       </c>
       <c r="C5">
-        <v>0.31062179905761816</v>
+        <v>0.2940605838236479</v>
       </c>
       <c r="D5">
-        <v>-19.288333646676833</v>
+        <v>-20.721163550252506</v>
       </c>
       <c r="E5">
         <v>0.0</v>
       </c>
       <c r="F5">
-        <v>0.38680566413659484</v>
+        <v>0.33530940966157274</v>
       </c>
       <c r="G5">
-        <v>-15.489372192953663</v>
+        <v>-18.172103959869425</v>
       </c>
       <c r="H5">
         <v>0.0</v>
@@ -602,22 +602,22 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>4.140604416611269</v>
+        <v>4.184475186050326</v>
       </c>
       <c r="C6">
-        <v>0.2984300371062786</v>
+        <v>0.256465653773006</v>
       </c>
       <c r="D6">
-        <v>13.874623535755864</v>
+        <v>16.31592817396884</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.46757252980287445</v>
+        <v>0.28914175998867914</v>
       </c>
       <c r="G6">
-        <v>8.855533960382404</v>
+        <v>14.472054075530847</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -628,25 +628,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1.4303666361999972</v>
+        <v>1.5681037487260112</v>
       </c>
       <c r="C7">
-        <v>0.269422850228147</v>
+        <v>0.20225725220027202</v>
       </c>
       <c r="D7">
-        <v>5.309002688483045</v>
+        <v>7.753016179480669</v>
       </c>
       <c r="E7">
-        <v>1.1022670776128507e-7</v>
+        <v>8.881784197001252e-15</v>
       </c>
       <c r="F7">
-        <v>0.41441610842772164</v>
+        <v>0.20130755660557775</v>
       </c>
       <c r="G7">
-        <v>3.4515227741188723</v>
+        <v>7.78959208073048</v>
       </c>
       <c r="H7">
-        <v>0.0005574327108044397</v>
+        <v>6.661338147750939e-15</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -654,25 +654,25 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1.8616371281626956</v>
+        <v>1.591156728000082</v>
       </c>
       <c r="C8">
-        <v>0.270737175351567</v>
+        <v>0.19360852605183443</v>
       </c>
       <c r="D8">
-        <v>6.876178440383217</v>
+        <v>8.218422816638173</v>
       </c>
       <c r="E8">
-        <v>6.147971021164267e-12</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="F8">
-        <v>0.3677157724929804</v>
+        <v>0.22787593289830857</v>
       </c>
       <c r="G8">
-        <v>5.062706762729993</v>
+        <v>6.9825571650436125</v>
       </c>
       <c r="H8">
-        <v>4.133453832544376e-7</v>
+        <v>2.8985702726913587e-12</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -680,22 +680,22 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>4.212325735986811</v>
+        <v>4.460982372133614</v>
       </c>
       <c r="C9">
-        <v>0.2356429252239392</v>
+        <v>0.2206010979050944</v>
       </c>
       <c r="D9">
-        <v>17.875884590991642</v>
+        <v>20.22194093545622</v>
       </c>
       <c r="E9">
         <v>0.0</v>
       </c>
       <c r="F9">
-        <v>0.28412937930333726</v>
+        <v>0.24437900385744454</v>
       </c>
       <c r="G9">
-        <v>14.825379009784557</v>
+        <v>18.254360242567618</v>
       </c>
       <c r="H9">
         <v>0.0</v>
@@ -706,22 +706,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>-3.4099921099535893</v>
+        <v>-3.5334309667037593</v>
       </c>
       <c r="C10">
-        <v>0.1967769508018489</v>
+        <v>0.19698273510507838</v>
       </c>
       <c r="D10">
-        <v>-17.329225277951352</v>
+        <v>-17.937769849824086</v>
       </c>
       <c r="E10">
         <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.39160490863572234</v>
+        <v>0.34513298479253895</v>
       </c>
       <c r="G10">
-        <v>-8.707735870404074</v>
+        <v>-10.237882562362799</v>
       </c>
       <c r="H10">
         <v>0.0</v>
@@ -742,7 +742,7 @@
         <v>17</v>
       </c>
       <c r="B1">
-        <v>-3585.8615589522515</v>
+        <v>-3585.273208229484</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>6.527347087860107</v>
+        <v>6.958906888961792</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -806,7 +806,7 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>7187.723117904503</v>
+        <v>7186.546416458968</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -814,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>7242.282805114792</v>
+        <v>7241.106103669257</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -822,7 +822,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>0.4851349491474547</v>
+        <v>0.485219425700667</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MXL_swissmetro.xlsx
+++ b/examples/output/MXL_swissmetro.xlsx
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>6.958906888961792</v>
+        <v>6.816570997238159</v>
       </c>
     </row>
     <row r="7" spans="1:2">
